--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755175568_h_9.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755175568_h_9.xlsx
@@ -658,7 +658,7 @@
         <v>0.008438734620987253</v>
       </c>
       <c r="C2" t="n">
-        <v>57117420</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>57117420</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>40068338</v>
+        <v>4035924</v>
       </c>
       <c r="L2" t="n">
-        <v>21877106</v>
+        <v>1874840</v>
       </c>
       <c r="M2" t="n">
-        <v>5221093</v>
+        <v>377392</v>
       </c>
       <c r="N2" t="n">
-        <v>231043</v>
+        <v>7827</v>
       </c>
       <c r="O2" t="n">
-        <v>3105128</v>
+        <v>212646</v>
       </c>
       <c r="P2" t="n">
-        <v>1179177</v>
+        <v>67448</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999747276306152</v>
+        <v>0.9999869465827942</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8589237332344055</v>
+        <v>0.7595889568328857</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7372852563858032</v>
+        <v>0.5710927844047546</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6726655960083008</v>
+        <v>0.4534615278244019</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2909300923347473</v>
+        <v>0.06783729791641235</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7190904021263123</v>
+        <v>0.5017164349555969</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8251359462738037</v>
+        <v>0.6620662808418274</v>
       </c>
       <c r="X2" t="n">
-        <v>57117420</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>57117420</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>43513679</v>
+        <v>4801660</v>
       </c>
       <c r="AG2" t="n">
-        <v>26954665</v>
+        <v>3018155</v>
       </c>
       <c r="AH2" t="n">
-        <v>7220207</v>
+        <v>805700</v>
       </c>
       <c r="AI2" t="n">
-        <v>532493</v>
+        <v>59334</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4137274</v>
+        <v>460847</v>
       </c>
       <c r="AK2" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9561951160430908</v>
+        <v>0.9551666378974915</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114695191383362</v>
+        <v>0.9119651317596436</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580380082130432</v>
+        <v>0.8582442998886108</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6618042588233948</v>
+        <v>0.660926342010498</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019699692726135</v>
+        <v>0.9019715189933777</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314467906951904</v>
+        <v>0.9314685463905334</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002022102987121896</v>
       </c>
       <c r="C3" t="n">
-        <v>951</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>40068338</v>
+        <v>4035924</v>
       </c>
       <c r="E3" t="n">
-        <v>5226339</v>
+        <v>937632</v>
       </c>
       <c r="F3" t="n">
-        <v>128567</v>
+        <v>37076</v>
       </c>
       <c r="G3" t="n">
-        <v>10482</v>
+        <v>2505</v>
       </c>
       <c r="H3" t="n">
-        <v>7827</v>
+        <v>1976</v>
       </c>
       <c r="I3" t="n">
-        <v>369</v>
+        <v>105</v>
       </c>
       <c r="J3" t="n">
-        <v>90625137</v>
+        <v>10069537</v>
       </c>
       <c r="K3" t="n">
-        <v>95719993</v>
+        <v>10123398</v>
       </c>
       <c r="L3" t="n">
-        <v>110323658</v>
+        <v>11689147</v>
       </c>
       <c r="M3" t="n">
-        <v>136780346</v>
+        <v>15020509</v>
       </c>
       <c r="N3" t="n">
-        <v>146375520</v>
+        <v>16218571</v>
       </c>
       <c r="O3" t="n">
-        <v>141941352</v>
+        <v>15693408</v>
       </c>
       <c r="P3" t="n">
-        <v>145753299</v>
+        <v>16187887</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8817298412322998</v>
+        <v>0.8047342300415039</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7384693622589111</v>
+        <v>0.5649160742759705</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6198650598526001</v>
+        <v>0.4012093842029572</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2868780791759491</v>
+        <v>0.08708568662405014</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6765511035919189</v>
+        <v>0.4158106744289398</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6773734092712402</v>
+        <v>0.3482337296009064</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>43513679</v>
+        <v>4801660</v>
       </c>
       <c r="Z3" t="n">
-        <v>1789967</v>
+        <v>198183</v>
       </c>
       <c r="AA3" t="n">
-        <v>77049</v>
+        <v>8469</v>
       </c>
       <c r="AB3" t="n">
-        <v>61571</v>
+        <v>6873</v>
       </c>
       <c r="AC3" t="n">
-        <v>337</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>90626580</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>100307692</v>
+        <v>11175395</v>
       </c>
       <c r="AG3" t="n">
-        <v>115500975</v>
+        <v>12805854</v>
       </c>
       <c r="AH3" t="n">
-        <v>138126469</v>
+        <v>15342287</v>
       </c>
       <c r="AI3" t="n">
-        <v>146666515</v>
+        <v>16295683</v>
       </c>
       <c r="AJ3" t="n">
-        <v>142704700</v>
+        <v>15854513</v>
       </c>
       <c r="AK3" t="n">
-        <v>145883883</v>
+        <v>16209047</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575468301773071</v>
+        <v>0.9574164748191833</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098641276359558</v>
+        <v>0.9094131588935852</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8572063446044922</v>
+        <v>0.8565481305122375</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6611781120300293</v>
+        <v>0.6601688861846924</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.901436984539032</v>
+        <v>0.9011460542678833</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312204718589783</v>
+        <v>0.931006908416748</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03192845045564235</v>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>6139759</v>
+        <v>1171675</v>
       </c>
       <c r="E4" t="n">
-        <v>21877106</v>
+        <v>1874840</v>
       </c>
       <c r="F4" t="n">
-        <v>1391423</v>
+        <v>224286</v>
       </c>
       <c r="G4" t="n">
-        <v>68124</v>
+        <v>15676</v>
       </c>
       <c r="H4" t="n">
-        <v>136558</v>
+        <v>29500</v>
       </c>
       <c r="I4" t="n">
-        <v>11930</v>
+        <v>2813</v>
       </c>
       <c r="J4" t="n">
-        <v>1443</v>
+        <v>83</v>
       </c>
       <c r="K4" t="n">
-        <v>6581134</v>
+        <v>1277376</v>
       </c>
       <c r="L4" t="n">
-        <v>7795407</v>
+        <v>1408059</v>
       </c>
       <c r="M4" t="n">
-        <v>2540703</v>
+        <v>454855</v>
       </c>
       <c r="N4" t="n">
-        <v>563110</v>
+        <v>107552</v>
       </c>
       <c r="O4" t="n">
-        <v>1213005</v>
+        <v>211191</v>
       </c>
       <c r="P4" t="n">
-        <v>249893</v>
+        <v>34427</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999873638153076</v>
+        <v>0.9999935030937195</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8701774477958679</v>
+        <v>0.7815101146697998</v>
       </c>
       <c r="S4" t="n">
-        <v>0.737876832485199</v>
+        <v>0.5679876208305359</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6451869010925293</v>
+        <v>0.4257381856441498</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2888898849487305</v>
+        <v>0.07626572996377945</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6971724033355713</v>
+        <v>0.4547419846057892</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7439889311790466</v>
+        <v>0.4564065933227539</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1861428</v>
+        <v>210622</v>
       </c>
       <c r="Z4" t="n">
-        <v>26954665</v>
+        <v>3018155</v>
       </c>
       <c r="AA4" t="n">
-        <v>748119</v>
+        <v>83217</v>
       </c>
       <c r="AB4" t="n">
-        <v>49825</v>
+        <v>5601</v>
       </c>
       <c r="AC4" t="n">
-        <v>10286</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1993435</v>
+        <v>225379</v>
       </c>
       <c r="AG4" t="n">
-        <v>2618090</v>
+        <v>291352</v>
       </c>
       <c r="AH4" t="n">
-        <v>1194580</v>
+        <v>133077</v>
       </c>
       <c r="AI4" t="n">
-        <v>272115</v>
+        <v>30440</v>
       </c>
       <c r="AJ4" t="n">
-        <v>449657</v>
+        <v>50086</v>
       </c>
       <c r="AK4" t="n">
-        <v>119309</v>
+        <v>13267</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568704962730408</v>
+        <v>0.9562901854515076</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106661081314087</v>
+        <v>0.9106873869895935</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576220273971558</v>
+        <v>0.857395350933075</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6614910364151001</v>
+        <v>0.6605474352836609</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.901703417301178</v>
+        <v>0.9015586376190186</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.931333601474762</v>
+        <v>0.9312376976013184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>178</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>307990</v>
+        <v>77984</v>
       </c>
       <c r="E5" t="n">
-        <v>2134350</v>
+        <v>368596</v>
       </c>
       <c r="F5" t="n">
-        <v>5221093</v>
+        <v>377392</v>
       </c>
       <c r="G5" t="n">
-        <v>186916</v>
+        <v>30614</v>
       </c>
       <c r="H5" t="n">
-        <v>523330</v>
+        <v>77010</v>
       </c>
       <c r="I5" t="n">
-        <v>49094</v>
+        <v>9036</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5374535</v>
+        <v>979302</v>
       </c>
       <c r="L5" t="n">
-        <v>7747829</v>
+        <v>1443954</v>
       </c>
       <c r="M5" t="n">
-        <v>3201858</v>
+        <v>563244</v>
       </c>
       <c r="N5" t="n">
-        <v>574327</v>
+        <v>82050</v>
       </c>
       <c r="O5" t="n">
-        <v>1484515</v>
+        <v>298755</v>
       </c>
       <c r="P5" t="n">
-        <v>561631</v>
+        <v>126238</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999902248382568</v>
+        <v>0.9999949336051941</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9190784692764282</v>
+        <v>0.8625317811965942</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8947961330413818</v>
+        <v>0.8262662887573242</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9611316919326782</v>
+        <v>0.9379813075065613</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9923012852668762</v>
+        <v>0.9884501695632935</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9817419052124023</v>
+        <v>0.968936026096344</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9945072531700134</v>
+        <v>0.9902129173278809</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>72813</v>
+        <v>8120</v>
       </c>
       <c r="Z5" t="n">
-        <v>771695</v>
+        <v>86892</v>
       </c>
       <c r="AA5" t="n">
-        <v>7220207</v>
+        <v>805700</v>
       </c>
       <c r="AB5" t="n">
-        <v>89834</v>
+        <v>10028</v>
       </c>
       <c r="AC5" t="n">
-        <v>262705</v>
+        <v>29263</v>
       </c>
       <c r="AD5" t="n">
-        <v>5697</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1929194</v>
+        <v>213566</v>
       </c>
       <c r="AG5" t="n">
-        <v>2670270</v>
+        <v>300639</v>
       </c>
       <c r="AH5" t="n">
-        <v>1202744</v>
+        <v>134936</v>
       </c>
       <c r="AI5" t="n">
-        <v>272877</v>
+        <v>30543</v>
       </c>
       <c r="AJ5" t="n">
-        <v>452369</v>
+        <v>50554</v>
       </c>
       <c r="AK5" t="n">
-        <v>119732</v>
+        <v>13363</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734498262405396</v>
+        <v>0.9732611179351807</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642059206962585</v>
+        <v>0.9639381766319275</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837738275527954</v>
+        <v>0.9836736917495728</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963112473487854</v>
+        <v>0.9962851405143738</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938946962356567</v>
+        <v>0.993869423866272</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998382031917572</v>
+        <v>0.998377799987793</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>114</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>113470</v>
+        <v>19211</v>
       </c>
       <c r="E6" t="n">
-        <v>165961</v>
+        <v>24743</v>
       </c>
       <c r="F6" t="n">
-        <v>203920</v>
+        <v>28106</v>
       </c>
       <c r="G6" t="n">
-        <v>231043</v>
+        <v>7827</v>
       </c>
       <c r="H6" t="n">
-        <v>83429</v>
+        <v>8937</v>
       </c>
       <c r="I6" t="n">
-        <v>7433</v>
+        <v>1040</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>58711</v>
+        <v>6601</v>
       </c>
       <c r="Z6" t="n">
-        <v>48403</v>
+        <v>5386</v>
       </c>
       <c r="AA6" t="n">
-        <v>98482</v>
+        <v>11048</v>
       </c>
       <c r="AB6" t="n">
-        <v>532493</v>
+        <v>59334</v>
       </c>
       <c r="AC6" t="n">
-        <v>62952</v>
+        <v>7027</v>
       </c>
       <c r="AD6" t="n">
-        <v>4329</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>19235</v>
+        <v>8208</v>
       </c>
       <c r="E7" t="n">
-        <v>248366</v>
+        <v>69895</v>
       </c>
       <c r="F7" t="n">
-        <v>764298</v>
+        <v>148732</v>
       </c>
       <c r="G7" t="n">
-        <v>271525</v>
+        <v>50480</v>
       </c>
       <c r="H7" t="n">
-        <v>3105128</v>
+        <v>212646</v>
       </c>
       <c r="I7" t="n">
-        <v>181067</v>
+        <v>21433</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>231</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>7296</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>267949</v>
+        <v>30010</v>
       </c>
       <c r="AB7" t="n">
-        <v>68492</v>
+        <v>7671</v>
       </c>
       <c r="AC7" t="n">
-        <v>4137274</v>
+        <v>460847</v>
       </c>
       <c r="AD7" t="n">
-        <v>108401</v>
+        <v>12055</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>141</v>
+        <v>47</v>
       </c>
       <c r="D8" t="n">
-        <v>680</v>
+        <v>298</v>
       </c>
       <c r="E8" t="n">
-        <v>20391</v>
+        <v>7193</v>
       </c>
       <c r="F8" t="n">
-        <v>52495</v>
+        <v>16655</v>
       </c>
       <c r="G8" t="n">
-        <v>26063</v>
+        <v>8277</v>
       </c>
       <c r="H8" t="n">
-        <v>461861</v>
+        <v>93768</v>
       </c>
       <c r="I8" t="n">
-        <v>1179177</v>
+        <v>67448</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>252</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>729</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2981</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2393</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>113377</v>
+        <v>12654</v>
       </c>
       <c r="AD8" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
